--- a/output/pdf_financials_xlsx/CGD.xlsx
+++ b/output/pdf_financials_xlsx/CGD.xlsx
@@ -5835,13 +5835,13 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0</v>
+        <v>0.576221</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>0.670355</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>0.8037069999999999</v>
       </c>
       <c r="E92" s="3" t="n">
         <v>0</v>
@@ -12458,7 +12458,11 @@
           <t>Reserves</t>
         </is>
       </c>
-      <c r="D46" t="inlineStr"/>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E46" t="inlineStr">
         <is>
           <t>-</t>
@@ -13890,7 +13894,11 @@
           <t>Reserves 670,355</t>
         </is>
       </c>
-      <c r="D61" t="inlineStr"/>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E61" s="5" t="n">
         <v>0.576221</v>
       </c>

--- a/output/pdf_financials_xlsx/CGD.xlsx
+++ b/output/pdf_financials_xlsx/CGD.xlsx
@@ -1059,10 +1059,10 @@
         <v>0</v>
       </c>
       <c r="P12" s="3" t="n">
-        <v>0</v>
+        <v>0.021764</v>
       </c>
       <c r="Q12" s="3" t="n">
-        <v>0</v>
+        <v>0.019694</v>
       </c>
     </row>
     <row r="13">
@@ -2006,10 +2006,10 @@
         <v>0.56323</v>
       </c>
       <c r="P27" s="3" t="n">
-        <v>-0.156142</v>
+        <v>-0.177906</v>
       </c>
       <c r="Q27" s="3" t="n">
-        <v>0.987079</v>
+        <v>0.9673850000000001</v>
       </c>
     </row>
     <row r="28">
@@ -2120,10 +2120,10 @@
         <v>0.56323</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>-0.156142</v>
+        <v>-0.177906</v>
       </c>
       <c r="Q29" s="3" t="n">
-        <v>0.987079</v>
+        <v>0.9673850000000001</v>
       </c>
     </row>
     <row r="30">
@@ -2371,7 +2371,7 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.463477</v>
       </c>
       <c r="C34" s="3" t="n">
         <v>0.089042</v>
@@ -2380,25 +2380,25 @@
         <v>1.35558</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.448738</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.121208</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.032338</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.236623</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>0.01629</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>0.047876</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>0.029141</v>
       </c>
       <c r="L34" s="1" t="inlineStr">
         <is>
@@ -2406,10 +2406,10 @@
         </is>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>0.018962</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0</v>
+        <v>0.19897</v>
       </c>
       <c r="O34" s="3" t="n">
         <v>0.747962</v>
@@ -2485,7 +2485,7 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.463477</v>
       </c>
       <c r="C36" s="3" t="n">
         <v>0.089042</v>
@@ -2494,25 +2494,25 @@
         <v>1.35558</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.448738</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>0.121208</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>0.032338</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>0.236623</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0.16</v>
+        <v>0.17629</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0.1075</v>
+        <v>0.155376</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0.158333</v>
+        <v>0.187474</v>
       </c>
       <c r="L36" s="1" t="inlineStr">
         <is>
@@ -2520,10 +2520,10 @@
         </is>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0.5075</v>
+        <v>0.526462</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>0.76629</v>
+        <v>0.96526</v>
       </c>
       <c r="O36" s="3" t="n">
         <v>1.922876</v>
@@ -3169,7 +3169,7 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>1.02532</v>
+        <v>0.561843</v>
       </c>
       <c r="C48" s="3" t="n">
         <v>0.262838</v>
@@ -3178,25 +3178,25 @@
         <v>0.15153</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0.578307</v>
+        <v>0.129569</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>0.47025</v>
+        <v>0.349042</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.09963</v>
+        <v>0.067292</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>0.363998</v>
+        <v>0.127375</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>0.023665</v>
+        <v>0.007375</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>0.048013</v>
+        <v>0.000137</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>0.029278</v>
+        <v>0.000137</v>
       </c>
       <c r="L48" s="1" t="inlineStr">
         <is>
@@ -3204,10 +3204,10 @@
         </is>
       </c>
       <c r="M48" s="3" t="n">
-        <v>0.018962</v>
+        <v>0</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>0.19897</v>
+        <v>0</v>
       </c>
       <c r="O48" s="3" t="n">
         <v>0</v>
@@ -10192,7 +10192,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -12648,7 +12648,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E48" s="5" t="n">
@@ -26192,7 +26192,7 @@
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E194" t="inlineStr">
